--- a/data/indicadores/03_03_01_05_vih.xlsx
+++ b/data/indicadores/03_03_01_05_vih.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pasantia\atlas ods 2025\Bases de datos indicadores\Finales y con codigo correcto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC78E7FD-93CB-4BEA-BDEA-86696F4F77A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5EBB29-C952-4CD2-886C-D186040466C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{A742A55C-A9B8-4C0F-89F2-B12936A81784}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3474" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3478" uniqueCount="607">
   <si>
     <t>NUMERO DE CASOS NOTIFICADOS DE VIH/SIDA, POR DEPARTAMENTO Y MUNICIPIO, AÑOS 2020 - 2024</t>
   </si>
@@ -1869,6 +1869,18 @@
   <si>
     <t>Bolivia</t>
   </si>
+  <si>
+    <t>Promedio nacional</t>
+  </si>
+  <si>
+    <t>10% prom nacional</t>
+  </si>
+  <si>
+    <t>25% prom nacional</t>
+  </si>
+  <si>
+    <t>50% prom nacional</t>
+  </si>
 </sst>
 </file>
 
@@ -2027,7 +2039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2101,6 +2113,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2128,17 +2141,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>529652</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>150000</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>71770</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>108000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="6" name="Imagen 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00ABA3E4-0A44-4A0C-A303-D58187ADABBC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24493E39-C4F3-493C-A704-C472F2B57931}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2161,7 +2174,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1" y="0"/>
-          <a:ext cx="5863651" cy="3960000"/>
+          <a:ext cx="6929769" cy="4680000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -21419,7 +21432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19992A1-CD13-4C25-BA56-E6957B9A825E}">
-  <dimension ref="A1:Y349"/>
+  <dimension ref="A1:Y353"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -50666,6 +50679,42 @@
       </c>
     </row>
     <row r="346" spans="1:25">
+      <c r="F346" s="34">
+        <f>SUM(F2:F344)</f>
+        <v>9897541</v>
+      </c>
+      <c r="G346" s="34">
+        <f t="shared" ref="G346:K346" si="48">SUM(G2:G344)</f>
+        <v>10059856</v>
+      </c>
+      <c r="H346" s="34">
+        <f t="shared" si="48"/>
+        <v>10168656</v>
+      </c>
+      <c r="I346" s="34">
+        <f t="shared" si="48"/>
+        <v>11147781</v>
+      </c>
+      <c r="J346" s="34">
+        <f t="shared" si="48"/>
+        <v>11256556</v>
+      </c>
+      <c r="K346" s="34">
+        <f t="shared" si="48"/>
+        <v>11365333</v>
+      </c>
+      <c r="L346" s="34">
+        <f>SUM(L2:L344)</f>
+        <v>1386</v>
+      </c>
+      <c r="M346" s="34">
+        <f t="shared" ref="M346:N346" si="49">SUM(M2:M344)</f>
+        <v>1550</v>
+      </c>
+      <c r="N346" s="34">
+        <f t="shared" si="49"/>
+        <v>1746</v>
+      </c>
       <c r="T346" t="s">
         <v>589</v>
       </c>
@@ -50684,6 +50733,18 @@
       </c>
     </row>
     <row r="348" spans="1:25">
+      <c r="L348" s="17">
+        <f>(L346/F346)*1000000</f>
+        <v>140.03478237675398</v>
+      </c>
+      <c r="M348" s="17">
+        <f t="shared" ref="M348:N348" si="50">(M346/G346)*1000000</f>
+        <v>154.07775220639343</v>
+      </c>
+      <c r="N348" s="17">
+        <f>(N346/H346)*1000000</f>
+        <v>171.70410720944832</v>
+      </c>
       <c r="T348" t="s">
         <v>591</v>
       </c>
@@ -50699,6 +50760,42 @@
       <c r="U349" s="17">
         <f>U347-U346</f>
         <v>553.13984571429307</v>
+      </c>
+    </row>
+    <row r="350" spans="1:25">
+      <c r="M350" t="s">
+        <v>603</v>
+      </c>
+      <c r="N350" s="17">
+        <f>AVERAGE(L348:N348)</f>
+        <v>155.27221393086526</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25">
+      <c r="M351" t="s">
+        <v>604</v>
+      </c>
+      <c r="N351">
+        <f>N350*0.1</f>
+        <v>15.527221393086528</v>
+      </c>
+    </row>
+    <row r="352" spans="1:25">
+      <c r="M352" t="s">
+        <v>605</v>
+      </c>
+      <c r="N352">
+        <f>N350*0.25</f>
+        <v>38.818053482716316</v>
+      </c>
+    </row>
+    <row r="353" spans="13:14">
+      <c r="M353" t="s">
+        <v>606</v>
+      </c>
+      <c r="N353">
+        <f>N350*0.5</f>
+        <v>77.636106965432631</v>
       </c>
     </row>
   </sheetData>
@@ -60786,7 +60883,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72403F32-E9AF-4D5E-BABE-7FFB89DFFC19}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10" ht="48">
@@ -60831,27 +60928,37 @@
       <c r="C2" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="15">
-        <v>0</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="15">
-        <v>353.65</v>
-      </c>
-      <c r="G2" s="15">
-        <v>353.65</v>
+      <c r="D2" s="31">
+        <v>15.526999999999999</v>
+      </c>
+      <c r="E2" s="31">
+        <v>15.526999999999999</v>
+      </c>
+      <c r="F2" s="31">
+        <v>77.635999999999996</v>
+      </c>
+      <c r="G2" s="31">
+        <v>77.635999999999996</v>
       </c>
       <c r="H2" s="15">
-        <v>707.3</v>
+        <v>155.27199999999999</v>
       </c>
       <c r="I2" s="15">
-        <v>707.3</v>
+        <v>155.27199999999999</v>
       </c>
       <c r="J2" s="15">
         <v>11516.4</v>
       </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="D4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="H4" s="39"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="D6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="H6" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
